--- a/healthcare_forms/029_hospice_spiritual_assessment_form--healthcare_forms.xlsx
+++ b/healthcare_forms/029_hospice_spiritual_assessment_form--healthcare_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -753,7 +753,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C38"/>
+  <dimension ref="A1:C36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1058,12 +1058,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>pagan</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Pagan</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>other_-_specify</t>
+          <t>pentecostal</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Other - specify</t>
+          <t>Pentecostal</t>
         </is>
       </c>
     </row>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>pagan</t>
+          <t>protestant</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Pagan</t>
+          <t>Protestant</t>
         </is>
       </c>
     </row>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>pentecostal</t>
+          <t>sikh</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Pentecostal</t>
+          <t>Sikh</t>
         </is>
       </c>
     </row>
@@ -1126,12 +1126,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>protestant</t>
+          <t>taoist</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Protestant</t>
+          <t>Taoist</t>
         </is>
       </c>
     </row>
@@ -1143,46 +1143,46 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>sikh</t>
+          <t>unitarian-unitarian</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sikh</t>
+          <t>Unitarian-Unitarian</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>religious_practice_choices</t>
+          <t>spiritual_leadership_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>taoist</t>
+          <t>yes_-_actively_seeking</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Taoist</t>
+          <t>Yes - actively seeking</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>religious_practice_choices</t>
+          <t>spiritual_leadership_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>unitarian-unitarian</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Unitarian-Unitarian</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1194,12 +1194,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>yes_-_actively_seeking</t>
+          <t>yes_-_actively_involved</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Yes - actively seeking</t>
+          <t>Yes - actively involved</t>
         </is>
       </c>
     </row>
@@ -1211,46 +1211,46 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes_-_actively_involved_-_with_a_specific_spiritual_leader</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes - actively involved - with a specific spiritual leader</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>spiritual_leadership_choices</t>
+          <t>spiritual_growth_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>yes_-_actively_involved</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Yes - actively involved</t>
+          <t>Not applicable</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>spiritual_leadership_choices</t>
+          <t>spiritual_growth_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>yes_-_actively_involved_-_with_a_specific_spiritual_leader</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Yes - actively involved - with a specific spiritual leader</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1262,12 +1262,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>yes_-_somewhat</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Yes - somewhat</t>
         </is>
       </c>
     </row>
@@ -1279,12 +1279,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>yes_-_somewhat_frequently</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Yes - somewhat frequently</t>
         </is>
       </c>
     </row>
@@ -1296,46 +1296,46 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>yes_-_somewhat</t>
+          <t>yes_-_very_frequently</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Yes - somewhat</t>
+          <t>Yes - very frequently</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>spiritual_growth_choices</t>
+          <t>patient_awareness_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>yes_-_somewhat_frequently</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Yes - somewhat frequently</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>spiritual_growth_choices</t>
+          <t>patient_awareness_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>yes_-_very_frequently</t>
+          <t>some</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Yes - very frequently</t>
+          <t>Some</t>
         </is>
       </c>
     </row>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>almost_all</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Almost all</t>
         </is>
       </c>
     </row>
@@ -1364,44 +1364,10 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>some</t>
+          <t>completely</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
-        <is>
-          <t>Some</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>patient_awareness_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>almost_all</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Almost all</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>patient_awareness_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>completely</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
         <is>
           <t>Completely</t>
         </is>
